--- a/artfynd/A 63026-2025 artfynd.xlsx
+++ b/artfynd/A 63026-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130236760</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>631809</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6664417</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130236761</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>631773</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6664404</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63026-2025 artfynd.xlsx
+++ b/artfynd/A 63026-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130236760</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130236761</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63026-2025 artfynd.xlsx
+++ b/artfynd/A 63026-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130236760</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130236761</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63026-2025 artfynd.xlsx
+++ b/artfynd/A 63026-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130236760</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>130236761</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63026-2025 artfynd.xlsx
+++ b/artfynd/A 63026-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75098981</v>
+        <v>130236755</v>
       </c>
       <c r="B2" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långsveden 3,5 km SO om Sörsjön, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631767.1696850769</v>
+        <v>631733</v>
       </c>
       <c r="R2" t="n">
-        <v>6664412.473249168</v>
+        <v>6664391</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,32 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Björklinge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kläckhål i fnösktickor på björkhögstubbe, omkr. 110 cm.</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130236760</v>
+        <v>130236769</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631809</v>
+        <v>631880</v>
       </c>
       <c r="R3" t="n">
-        <v>6664417</v>
+        <v>6664416</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -904,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130236761</v>
+        <v>130236760</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631773</v>
+        <v>631809</v>
       </c>
       <c r="R4" t="n">
-        <v>6664404</v>
+        <v>6664417</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -998,6 +963,317 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130236761</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>631773</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6664404</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>75098981</v>
+      </c>
+      <c r="B6" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långsveden 3,5 km SO om Sörsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631767</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6664412</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Björklinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2004-06-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2004-06-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kläckhål i fnösktickor på björkhögstubbe, omkr. 110 cm.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130236775</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>631783</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6664373</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
